--- a/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Captures if patient data is transferred outside the EU by this device.</t>
+    <t>Documents whether use of the AI system involves a transfer of personal data to a third country or an international organisation and identifies the destination country or countries where applicable.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>79</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-third-country-data-transfer.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="126">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/StructureDefinition/third-country-data-transfer</t>
+    <t>http://example.org/fhir/trust-ai-transparency/StructureDefinition/third-country-data-transfer</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:39:53+00:00</t>
+    <t>2026-09-09T11:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -396,6 +396,12 @@
   <si>
     <t xml:space="preserve">code
 </t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
   </si>
   <si>
     <t>base64Binary
@@ -744,7 +750,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="31.83984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2175,13 +2181,11 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -2350,7 +2354,7 @@
         <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>111</v>
